--- a/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
+++ b/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parks\OneDrive\Documents\UC\Summer Research\DetectRTL\CWE_Examples\CWE-1233\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parks\OneDrive\Documents\UC\Research\DetectRTL\CWE_Examples\CWE-1233\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278CF804-1647-47A1-9CF7-3D006C44F229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EF08C7-652A-4032-986F-29856C98A7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
+++ b/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parks\OneDrive\Documents\UC\Research\DetectRTL\CWE_Examples\CWE-1233\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EF08C7-652A-4032-986F-29856C98A7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E569258-5A1E-4411-8896-FBBEECC8555F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Detailed Results" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="98">
   <si>
     <t>File Name</t>
   </si>
@@ -193,13 +194,139 @@
   </si>
   <si>
     <t>Secure: All security sensitive register assignments are protected</t>
+  </si>
+  <si>
+    <t>rdata is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>Assignment Missing Lock Bit Protection</t>
+  </si>
+  <si>
+    <t>CWE-1233</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_9_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>data is assigned without correct lock bit enforcement</t>
+  </si>
+  <si>
+    <t>Incorrect Lock Enforcement</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_8_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>newMessage is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>startHash is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_6_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_5_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>acct_mem is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_4_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>key_reg2 is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_3_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>key_reg1 is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>key_reg0 is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_2_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_1_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>end_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>key_sel is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_10_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>start is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>state is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>p_c is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Line Number</t>
+  </si>
+  <si>
+    <t>Vulnerability Type</t>
+  </si>
+  <si>
+    <t>Related CWE</t>
+  </si>
+  <si>
+    <t>start_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>length_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>source_addr_lsb_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>dest_addr_lsb_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>dest_addr_mdb_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>done_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>core_lock_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>source_addr_msb_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>block_reg is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>fuse_req_o is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>fuse_addr_o is assigned without lock bit protection</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_7_vulnerable_parsed.json</t>
+  </si>
+  <si>
+    <t>msg_in is assigned without lock bit protection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,16 +342,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -232,11 +376,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -256,6 +415,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1764,4 +1928,2020 @@
     <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A906EDC6-4E6A-459E-A629-5A5E7FE38FCA}">
+  <dimension ref="A1:E126"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="9">
+        <v>108</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="9">
+        <v>120</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="9">
+        <v>102</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="9">
+        <v>144</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="9">
+        <v>132</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="9">
+        <v>134</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="9">
+        <v>136</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="9">
+        <v>138</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="9">
+        <v>140</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="9">
+        <v>142</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="9">
+        <v>144</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="9">
+        <v>146</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="9">
+        <v>148</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="9">
+        <v>163</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="9">
+        <v>165</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="9">
+        <v>167</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="9">
+        <v>169</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="9">
+        <v>171</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="9">
+        <v>173</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="9">
+        <v>175</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="9">
+        <v>177</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="9">
+        <v>179</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="9">
+        <v>181</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="9">
+        <v>133</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="9">
+        <v>259</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="9">
+        <v>262</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="9">
+        <v>264</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="9">
+        <v>266</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="9">
+        <v>83</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="9">
+        <v>85</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="9">
+        <v>99</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="9">
+        <v>101</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="9">
+        <v>108</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="9">
+        <v>139</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="9">
+        <v>156</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="9">
+        <v>158</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="9">
+        <v>160</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="9">
+        <v>162</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="9">
+        <v>218</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="9">
+        <v>220</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="9">
+        <v>222</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="9">
+        <v>224</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="9">
+        <v>226</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="9">
+        <v>228</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="9">
+        <v>230</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="9">
+        <v>232</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="9">
+        <v>234</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="9">
+        <v>236</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="9">
+        <v>238</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="9">
+        <v>240</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="9">
+        <v>242</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="9">
+        <v>244</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="9">
+        <v>246</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="9">
+        <v>248</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="9">
+        <v>250</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="9">
+        <v>252</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="9">
+        <v>254</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="9">
+        <v>256</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="9">
+        <v>258</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="9">
+        <v>260</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="9">
+        <v>262</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="9">
+        <v>264</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="9">
+        <v>266</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" s="9">
+        <v>268</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" s="9">
+        <v>270</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="9">
+        <v>272</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" s="9">
+        <v>274</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="9">
+        <v>276</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="9">
+        <v>278</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" s="9">
+        <v>280</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="9">
+        <v>282</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="9">
+        <v>284</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="9">
+        <v>286</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="9">
+        <v>288</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="9">
+        <v>290</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="9">
+        <v>292</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85" s="9">
+        <v>294</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" s="9">
+        <v>296</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" s="9">
+        <v>298</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" s="9">
+        <v>300</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="9">
+        <v>302</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90" s="9">
+        <v>304</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="9">
+        <v>306</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92" s="9">
+        <v>308</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="9">
+        <v>310</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="9">
+        <v>312</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" s="9">
+        <v>314</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="9">
+        <v>316</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="9">
+        <v>318</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D98" s="9">
+        <v>320</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D99" s="9">
+        <v>322</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="9">
+        <v>324</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101" s="9">
+        <v>326</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102" s="9">
+        <v>328</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103" s="9">
+        <v>330</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" s="9">
+        <v>332</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D105" s="9">
+        <v>334</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D106" s="9">
+        <v>336</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D107" s="9">
+        <v>338</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D108" s="9">
+        <v>340</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D109" s="9">
+        <v>342</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110" s="9">
+        <v>344</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D112" s="9">
+        <v>122</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" s="9">
+        <v>123</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D114" s="9">
+        <v>126</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D115" s="9">
+        <v>138</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D117" s="9">
+        <v>170</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D118" s="9">
+        <v>172</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D119" s="9">
+        <v>174</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D120" s="9">
+        <v>176</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D121" s="9">
+        <v>178</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D122" s="9">
+        <v>180</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" s="9">
+        <v>182</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D124" s="9">
+        <v>184</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D125" s="9">
+        <v>186</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D126" s="9">
+        <v>188</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
+++ b/CWE_Examples/CWE-1233/CWE-1233-vulnerability-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parks\OneDrive\Documents\UC\Research\DetectRTL\CWE_Examples\CWE-1233\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2895F5-B4D2-4CAF-988B-89A52DF2E2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFEA5B8-BCD7-4B35-B2F3-E32F6D2E1061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9690" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,29 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="143">
   <si>
     <t>File Name</t>
   </si>
   <si>
-    <t>Case Number</t>
-  </si>
-  <si>
-    <t>Unreachable States</t>
-  </si>
-  <si>
-    <t>State Coverage</t>
-  </si>
-  <si>
-    <t>Deadlocks</t>
-  </si>
-  <si>
-    <t>Secure: All states reachable</t>
-  </si>
-  <si>
-    <t>Secure: No deadlocks</t>
-  </si>
-  <si>
     <t>Lock Enforcment Completeness</t>
   </si>
   <si>
@@ -72,36 +54,6 @@
     <t>Lock Enforcement Completeness</t>
   </si>
   <si>
-    <t>CWE_1233_example_1_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_10_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_9_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_8_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_7_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_6_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_5_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_4_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_3_fixed_parsed.v</t>
-  </si>
-  <si>
-    <t>CWE_1233_example_2_fixed_parsed.v</t>
-  </si>
-  <si>
     <t>CWE_1233_example_1_vulnerable_parsed.v</t>
   </si>
   <si>
@@ -132,24 +84,12 @@
     <t>CWE_1233_example_2_vulnerable_parsed.v</t>
   </si>
   <si>
-    <t>CWE-1245 Vulnerabilities in CWE-1233 Vulnerable Examples</t>
-  </si>
-  <si>
-    <t>CWE-1245 Vulnerabilities in CWE-1233 Secure Examples</t>
-  </si>
-  <si>
-    <t>CWE-1233 Vulnerabilities in CWE-1233 Fixed Examples</t>
-  </si>
-  <si>
     <t>CWE-1233 Vulnerabilities in CWE-1233 Vulnerable Examples</t>
   </si>
   <si>
     <t>Security Sensitive Registers</t>
   </si>
   <si>
-    <t>Secure: Default state covers rest of possible values</t>
-  </si>
-  <si>
     <t>start_reg, length_reg, source_addr_lsb_reg, source_addr_msb_reg, dest_addr_lsb_reg, dest_addr_msb_reg, done_reg, core_lock_reg, end_reg, rdata</t>
   </si>
   <si>
@@ -453,9 +393,6 @@
     <t>key2</t>
   </si>
   <si>
-    <t>Total CWE-1233 Vulnerable Registers</t>
-  </si>
-  <si>
     <t>File</t>
   </si>
   <si>
@@ -487,6 +424,48 @@
   </si>
   <si>
     <t>Example 10</t>
+  </si>
+  <si>
+    <t>CWE-1233 Vulnerabilities in CWE-1233 Secure Examples</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_1_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_2_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_3_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_4_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_5_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_6_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_7_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_8_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_9_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>CWE_1233_example_10_secure_parsed.v</t>
+  </si>
+  <si>
+    <t>Total Security-Sensitve Registers</t>
+  </si>
+  <si>
+    <t>Total Vulnerable Registers</t>
+  </si>
+  <si>
+    <t>Total Secure Registers</t>
   </si>
 </sst>
 </file>
@@ -580,67 +559,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="13">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -689,55 +626,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F94C13D-904B-4ABD-9F7E-53C3DC390700}" name="Table1" displayName="Table1" ref="A86:E106" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="A86:E106" xr:uid="{5F94C13D-904B-4ABD-9F7E-53C3DC390700}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BB050F11-09FF-49AD-AD1D-5BF90F642601}" name="Table1410" displayName="Table1410" ref="A2:E69" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A2:E69" xr:uid="{BB050F11-09FF-49AD-AD1D-5BF90F642601}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B9661404-79CE-40A3-9E22-450B66FCA9A1}" name="File Name" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{C8557D32-6F96-41D5-811F-33B42706893F}" name="Case Number" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{EF0A8365-2E22-43CB-9B9A-1439EC7CA8E5}" name="State Coverage" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{0B41959F-D795-4C04-84EF-054AD8E21F8B}" name="Unreachable States" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{9A2B96AD-6AE4-4701-87A4-A968E160A7E1}" name="Deadlocks" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{C75F07A5-0434-4D14-A280-5B8A059959F4}" name="File Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{6F06D4D5-C66E-42DF-ACA1-FF53DDEB3BD2}" name="Security Sensitive Registers" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{2CC531AD-7826-4282-AC40-83969E3A436D}" name="Assignment Line Numbers" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{E2CF98F7-C2D6-48D7-8774-AF3E821F437C}" name="Lock Enforcment Completeness" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{32739EC9-7CD0-44C1-875D-B423B3946704}" name="Security Sensitive Registers Coverage Completeness" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7E831A8D-7049-44E1-B3F8-69447E945B54}" name="Table13" displayName="Table13" ref="A109:E129" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A109:E129" xr:uid="{7E831A8D-7049-44E1-B3F8-69447E945B54}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9D6653A0-D914-486B-AA04-6BC34EA1755E}" name="File Name" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{835B414E-60F3-4563-AE19-85BB73F98EC7}" name="Case Number" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{4A9AED78-B318-45AE-9A61-6224AD9CFCC4}" name="State Coverage" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{2B03A665-DA4A-4154-82A1-BAF7C4C383F3}" name="Unreachable States" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{58544891-3CF4-4016-8E58-34CB9D6A312A}" name="Deadlocks" dataDxfId="13"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BB050F11-09FF-49AD-AD1D-5BF90F642601}" name="Table1410" displayName="Table1410" ref="A2:E69" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A2:E69" xr:uid="{BB050F11-09FF-49AD-AD1D-5BF90F642601}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C75F07A5-0434-4D14-A280-5B8A059959F4}" name="File Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{6F06D4D5-C66E-42DF-ACA1-FF53DDEB3BD2}" name="Security Sensitive Registers" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{2CC531AD-7826-4282-AC40-83969E3A436D}" name="Assignment Line Numbers" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E2CF98F7-C2D6-48D7-8774-AF3E821F437C}" name="Lock Enforcment Completeness" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{32739EC9-7CD0-44C1-875D-B423B3946704}" name="Security Sensitive Registers Coverage Completeness" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E2F09405-F2BB-46A7-8062-3903ABFBB844}" name="Table211" displayName="Table211" ref="A72:D82" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E2F09405-F2BB-46A7-8062-3903ABFBB844}" name="Table211" displayName="Table211" ref="A72:D82" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A72:D82" xr:uid="{E2F09405-F2BB-46A7-8062-3903ABFBB844}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E44F1D28-6BE6-4688-A916-575F3DFEC47F}" name="File Name" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{84744B2C-540E-4C8D-959B-E05E67E93189}" name="Security Sensitive Registers" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F13F89C7-8737-44A8-AF1E-5BA4F673DDA2}" name="Lock Enforcement Completeness" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{04CF0FC2-EC06-4CF5-AD9F-B74BA3DF83D8}" name="Security Sensitive Registers Coverage Completeness" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{E44F1D28-6BE6-4688-A916-575F3DFEC47F}" name="File Name" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{84744B2C-540E-4C8D-959B-E05E67E93189}" name="Security Sensitive Registers" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F13F89C7-8737-44A8-AF1E-5BA4F673DDA2}" name="Lock Enforcement Completeness" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{04CF0FC2-EC06-4CF5-AD9F-B74BA3DF83D8}" name="Security Sensitive Registers Coverage Completeness" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1006,1944 +915,1426 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="32.88671875" style="1" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="1"/>
     <col min="7" max="7" width="26.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.109375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="29.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="7">
+        <v>10</v>
+      </c>
+      <c r="I4" s="7">
+        <v>10</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="7">
+        <v>8</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H4" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H5" s="9">
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="7">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7">
+        <v>4</v>
+      </c>
+      <c r="J6" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="7">
+        <v>5</v>
+      </c>
+      <c r="I9" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="J9" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="9">
+    <row r="10" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="7">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
+      <c r="I11" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H8" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="J11" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="9">
+    <row r="12" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="7">
+        <v>8</v>
+      </c>
+      <c r="I12" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="J12" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="7">
+        <v>8</v>
+      </c>
+      <c r="I13" s="7">
+        <v>4</v>
+      </c>
+      <c r="J13" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="1">
+        <f>SUM(H4:H13)</f>
+        <v>70</v>
+      </c>
+      <c r="I14" s="1">
+        <f>SUM(I4:I13)</f>
         <v>30</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H13" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J14" s="1">
+        <f>SUM(J4:J13)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-    </row>
-    <row r="72" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+    </row>
+    <row r="72" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C75" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B87" s="1">
-        <v>1</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="1">
-        <v>2</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B89" s="1">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B90" s="1">
-        <v>2</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B91" s="1">
-        <v>1</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B92" s="1">
-        <v>2</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B93" s="1">
-        <v>1</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B94" s="1">
-        <v>2</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B95" s="1">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B96" s="1">
-        <v>2</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B97" s="1">
-        <v>1</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B98" s="1">
-        <v>2</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B100" s="1">
-        <v>2</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B102" s="1">
-        <v>2</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" s="1">
-        <v>1</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B104" s="1">
-        <v>2</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B105" s="1">
-        <v>1</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" s="1">
-        <v>2</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A110" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B110" s="1">
-        <v>1</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B111" s="1">
-        <v>2</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B112" s="1">
-        <v>1</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B113" s="1">
-        <v>2</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B114" s="1">
-        <v>1</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B115" s="1">
-        <v>2</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B116" s="1">
-        <v>1</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B117" s="1">
-        <v>2</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B118" s="1">
-        <v>1</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B119" s="1">
-        <v>2</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B120" s="1">
-        <v>1</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B121" s="1">
-        <v>2</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B122" s="1">
-        <v>1</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B123" s="1">
-        <v>2</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B124" s="1">
-        <v>1</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B125" s="1">
-        <v>2</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B126" s="1">
-        <v>1</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B127" s="1">
-        <v>2</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128" s="1">
-        <v>1</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129" s="1">
-        <v>2</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C87" s="4"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C90" s="4"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C91" s="4"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C92" s="4"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C93" s="4"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C94" s="4"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C95" s="4"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C96" s="4"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C98" s="4"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C99" s="4"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C100" s="4"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C101" s="4"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C102" s="4"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C103" s="4"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C104" s="4"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C105" s="4"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C106" s="4"/>
+    </row>
+    <row r="108" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C110" s="4"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C111" s="4"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C112" s="4"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C113" s="4"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C114" s="4"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C115" s="4"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C116" s="4"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C117" s="4"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C118" s="4"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C119" s="4"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C120" s="4"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C121" s="4"/>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="4"/>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C123" s="4"/>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C124" s="4"/>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C125" s="4"/>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C126" s="4"/>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C127" s="4"/>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C128" s="4"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C129" s="4"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -2956,20 +2347,16 @@
       <c r="D151" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A85:E85"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A108:E108"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="4">
+  <tableParts count="2">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2991,1997 +2378,1997 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>169</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>175</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>177</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>179</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>259</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>262</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>264</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>266</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>101</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>108</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>162</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>218</v>
       </c>
       <c r="E47" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>220</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>226</v>
       </c>
       <c r="E51" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>228</v>
       </c>
       <c r="E52" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>230</v>
       </c>
       <c r="E53" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>232</v>
       </c>
       <c r="E54" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>236</v>
       </c>
       <c r="E56" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>238</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>240</v>
       </c>
       <c r="E58" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>242</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>244</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>246</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>248</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>250</v>
       </c>
       <c r="E63" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>252</v>
       </c>
       <c r="E64" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>254</v>
       </c>
       <c r="E65" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D66">
         <v>256</v>
       </c>
       <c r="E66" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <v>258</v>
       </c>
       <c r="E67" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D68">
         <v>260</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>262</v>
       </c>
       <c r="E69" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D70">
         <v>264</v>
       </c>
       <c r="E70" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D71">
         <v>266</v>
       </c>
       <c r="E71" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D72">
         <v>268</v>
       </c>
       <c r="E72" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D73">
         <v>270</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D74">
         <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D75">
         <v>274</v>
       </c>
       <c r="E75" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D76">
         <v>276</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C77" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D77">
         <v>278</v>
       </c>
       <c r="E77" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D78">
         <v>280</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D79">
         <v>282</v>
       </c>
       <c r="E79" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D80">
         <v>284</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D81">
         <v>286</v>
       </c>
       <c r="E81" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D82">
         <v>288</v>
       </c>
       <c r="E82" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C83" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D83">
         <v>290</v>
       </c>
       <c r="E83" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C84" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D84">
         <v>292</v>
       </c>
       <c r="E84" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D85">
         <v>294</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D86">
         <v>296</v>
       </c>
       <c r="E86" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C87" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D87">
         <v>298</v>
       </c>
       <c r="E87" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D88">
         <v>300</v>
       </c>
       <c r="E88" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D89">
         <v>302</v>
       </c>
       <c r="E89" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C90" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D90">
         <v>304</v>
       </c>
       <c r="E90" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C91" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D91">
         <v>306</v>
       </c>
       <c r="E91" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C92" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D92">
         <v>308</v>
       </c>
       <c r="E92" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C93" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D93">
         <v>310</v>
       </c>
       <c r="E93" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C94" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D94">
         <v>312</v>
       </c>
       <c r="E94" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C95" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D95">
         <v>314</v>
       </c>
       <c r="E95" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D96">
         <v>316</v>
       </c>
       <c r="E96" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B97" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C97" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D97">
         <v>318</v>
       </c>
       <c r="E97" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D98">
         <v>320</v>
       </c>
       <c r="E98" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C99" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D99">
         <v>322</v>
       </c>
       <c r="E99" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C100" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D100">
         <v>324</v>
       </c>
       <c r="E100" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C101" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D101">
         <v>326</v>
       </c>
       <c r="E101" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D102">
         <v>328</v>
       </c>
       <c r="E102" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C103" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D103">
         <v>330</v>
       </c>
       <c r="E103" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C104" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D104">
         <v>332</v>
       </c>
       <c r="E104" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B105" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C105" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D105">
         <v>334</v>
       </c>
       <c r="E105" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B106" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C106" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D106">
         <v>336</v>
       </c>
       <c r="E106" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B107" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C107" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D107">
         <v>338</v>
       </c>
       <c r="E107" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C108" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D108">
         <v>340</v>
       </c>
       <c r="E108" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C109" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D109">
         <v>342</v>
       </c>
       <c r="E109" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C110" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D110">
         <v>344</v>
       </c>
       <c r="E110" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C112" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D112">
         <v>122</v>
       </c>
       <c r="E112" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C113" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D113">
         <v>123</v>
       </c>
       <c r="E113" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D114">
         <v>126</v>
       </c>
       <c r="E114" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D115">
         <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="116" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D117">
         <v>170</v>
       </c>
       <c r="E117" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B118" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D118">
         <v>172</v>
       </c>
       <c r="E118" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B119" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D119">
         <v>174</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C120" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D120">
         <v>176</v>
       </c>
       <c r="E120" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B121" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C121" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D121">
         <v>178</v>
       </c>
       <c r="E121" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B122" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C122" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D122">
         <v>180</v>
       </c>
       <c r="E122" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B123" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C123" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D123">
         <v>182</v>
       </c>
       <c r="E123" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B124" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D124">
         <v>184</v>
       </c>
       <c r="E124" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C125" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D125">
         <v>186</v>
       </c>
       <c r="E125" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C126" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D126">
         <v>188</v>
       </c>
       <c r="E126" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
